--- a/data/nzd0118/nzd0118.xlsx
+++ b/data/nzd0118/nzd0118.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I305"/>
+  <dimension ref="A1:I306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10491,6 +10491,39 @@
         <v>383.4</v>
       </c>
       <c r="I305" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:05:54+00:00</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>375.38</v>
+      </c>
+      <c r="C306" t="n">
+        <v>370.94</v>
+      </c>
+      <c r="D306" t="n">
+        <v>372</v>
+      </c>
+      <c r="E306" t="n">
+        <v>371.02</v>
+      </c>
+      <c r="F306" t="n">
+        <v>373.69</v>
+      </c>
+      <c r="G306" t="n">
+        <v>375.77</v>
+      </c>
+      <c r="H306" t="n">
+        <v>381.66</v>
+      </c>
+      <c r="I306" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -10507,7 +10540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B319"/>
+  <dimension ref="A1:B320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13700,6 +13733,16 @@
       </c>
       <c r="B319" t="n">
         <v>0.44</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>1.11</v>
       </c>
     </row>
   </sheetData>
@@ -13868,28 +13911,28 @@
         <v>0.0478</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1370381516889387</v>
+        <v>0.1285735020315475</v>
       </c>
       <c r="J2" t="n">
+        <v>305</v>
+      </c>
+      <c r="K2" t="n">
         <v>304</v>
       </c>
-      <c r="K2" t="n">
-        <v>303</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.02073947084816574</v>
+        <v>0.0182137850374452</v>
       </c>
       <c r="M2" t="n">
-        <v>5.432184171592561</v>
+        <v>5.445780503721712</v>
       </c>
       <c r="N2" t="n">
-        <v>43.87215175335086</v>
+        <v>44.24546691382827</v>
       </c>
       <c r="O2" t="n">
-        <v>6.623605645971902</v>
+        <v>6.651726611476772</v>
       </c>
       <c r="P2" t="n">
-        <v>384.4039618975149</v>
+        <v>384.4978886313349</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -13946,28 +13989,28 @@
         <v>0.0731</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1577500054023019</v>
+        <v>0.1491570181222614</v>
       </c>
       <c r="J3" t="n">
+        <v>305</v>
+      </c>
+      <c r="K3" t="n">
         <v>304</v>
       </c>
-      <c r="K3" t="n">
-        <v>303</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.05300161015376836</v>
+        <v>0.04687833394448537</v>
       </c>
       <c r="M3" t="n">
-        <v>3.903496286321178</v>
+        <v>3.926690812655828</v>
       </c>
       <c r="N3" t="n">
-        <v>21.99906966109813</v>
+        <v>22.46015098034869</v>
       </c>
       <c r="O3" t="n">
-        <v>4.690316584314766</v>
+        <v>4.739214173293785</v>
       </c>
       <c r="P3" t="n">
-        <v>379.6172525875404</v>
+        <v>379.7126034008214</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -14024,28 +14067,28 @@
         <v>0.0895</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04729159815805495</v>
+        <v>0.0370737730453006</v>
       </c>
       <c r="J4" t="n">
+        <v>305</v>
+      </c>
+      <c r="K4" t="n">
         <v>304</v>
       </c>
-      <c r="K4" t="n">
-        <v>303</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.004901219725248263</v>
+        <v>0.00293976182785427</v>
       </c>
       <c r="M4" t="n">
-        <v>3.871105568304377</v>
+        <v>3.904159543808001</v>
       </c>
       <c r="N4" t="n">
-        <v>22.46649765647061</v>
+        <v>23.14685215424266</v>
       </c>
       <c r="O4" t="n">
-        <v>4.739883717610655</v>
+        <v>4.811117557724262</v>
       </c>
       <c r="P4" t="n">
-        <v>385.9854011819145</v>
+        <v>386.09878176805</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14102,28 +14145,28 @@
         <v>0.0728</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03595549363909106</v>
+        <v>0.02687626950658366</v>
       </c>
       <c r="J5" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K5" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001868809170541441</v>
+        <v>0.001034023282532437</v>
       </c>
       <c r="M5" t="n">
-        <v>4.850023740351975</v>
+        <v>4.874816130442828</v>
       </c>
       <c r="N5" t="n">
-        <v>34.54260173903987</v>
+        <v>35.0343786838242</v>
       </c>
       <c r="O5" t="n">
-        <v>5.877295444253238</v>
+        <v>5.918984599052797</v>
       </c>
       <c r="P5" t="n">
-        <v>383.7369445567263</v>
+        <v>383.836971984041</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14180,28 +14223,28 @@
         <v>0.0607</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1261450197090682</v>
+        <v>-0.134150166799119</v>
       </c>
       <c r="J6" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K6" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02331539420338402</v>
+        <v>0.0261105296341545</v>
       </c>
       <c r="M6" t="n">
-        <v>4.708201092172303</v>
+        <v>4.727605333971325</v>
       </c>
       <c r="N6" t="n">
-        <v>32.45145923464616</v>
+        <v>32.79613393339429</v>
       </c>
       <c r="O6" t="n">
-        <v>5.696618227917872</v>
+        <v>5.726790893108835</v>
       </c>
       <c r="P6" t="n">
-        <v>388.7493132653477</v>
+        <v>388.8390040587905</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -14258,28 +14301,28 @@
         <v>0.0832</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.07995271189154413</v>
+        <v>-0.08614813191356865</v>
       </c>
       <c r="J7" t="n">
+        <v>305</v>
+      </c>
+      <c r="K7" t="n">
         <v>304</v>
       </c>
-      <c r="K7" t="n">
-        <v>303</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.012699265045931</v>
+        <v>0.01465006195834961</v>
       </c>
       <c r="M7" t="n">
-        <v>4.063156689980706</v>
+        <v>4.079365039568185</v>
       </c>
       <c r="N7" t="n">
-        <v>24.56103355950059</v>
+        <v>24.75700815541483</v>
       </c>
       <c r="O7" t="n">
-        <v>4.955908953915577</v>
+        <v>4.975641481800596</v>
       </c>
       <c r="P7" t="n">
-        <v>387.0751420051528</v>
+        <v>387.1439290566775</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -14336,28 +14379,28 @@
         <v>0.079</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.187457597527763</v>
+        <v>-0.1921783857859222</v>
       </c>
       <c r="J8" t="n">
+        <v>305</v>
+      </c>
+      <c r="K8" t="n">
         <v>304</v>
       </c>
-      <c r="K8" t="n">
-        <v>303</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.04405846535070335</v>
+        <v>0.0463157142530144</v>
       </c>
       <c r="M8" t="n">
-        <v>5.131867276841699</v>
+        <v>5.13932522329311</v>
       </c>
       <c r="N8" t="n">
-        <v>37.68056681372857</v>
+        <v>37.71731265920013</v>
       </c>
       <c r="O8" t="n">
-        <v>6.138449870588548</v>
+        <v>6.141442229574428</v>
       </c>
       <c r="P8" t="n">
-        <v>393.5803496607459</v>
+        <v>393.6327640416912</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -14395,7 +14438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I305"/>
+  <dimension ref="A1:I306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28705,6 +28748,53 @@
         </is>
       </c>
     </row>
+    <row r="306">
+      <c r="A306" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:05:54+00:00</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>-36.16857547041311,175.4843192978932</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>-36.168713969893496,175.48520332009554</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>-36.168803249295635,175.48608364596024</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>-36.16878092898966,175.4869613341157</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>-36.16867710983286,175.4878385059546</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>-36.16849920513441,175.4886911057751</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>-36.16823624790917,175.48952344292138</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0118/nzd0118.xlsx
+++ b/data/nzd0118/nzd0118.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I306"/>
+  <dimension ref="A1:I308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10524,6 +10524,72 @@
         <v>381.66</v>
       </c>
       <c r="I306" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>373.76</v>
+      </c>
+      <c r="C307" t="n">
+        <v>368.17</v>
+      </c>
+      <c r="D307" t="n">
+        <v>371.75</v>
+      </c>
+      <c r="E307" t="n">
+        <v>371.77</v>
+      </c>
+      <c r="F307" t="n">
+        <v>374.86</v>
+      </c>
+      <c r="G307" t="n">
+        <v>376.26</v>
+      </c>
+      <c r="H307" t="n">
+        <v>382.56</v>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:05:44+00:00</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>375.78</v>
+      </c>
+      <c r="C308" t="n">
+        <v>370.78</v>
+      </c>
+      <c r="D308" t="n">
+        <v>375.38</v>
+      </c>
+      <c r="E308" t="n">
+        <v>374.65</v>
+      </c>
+      <c r="F308" t="n">
+        <v>377.44</v>
+      </c>
+      <c r="G308" t="n">
+        <v>378.97</v>
+      </c>
+      <c r="H308" t="n">
+        <v>386.96</v>
+      </c>
+      <c r="I308" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -10540,7 +10606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B320"/>
+  <dimension ref="A1:B322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13743,6 +13809,26 @@
       </c>
       <c r="B320" t="n">
         <v>1.11</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -13911,28 +13997,28 @@
         <v>0.0478</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1285735020315475</v>
+        <v>0.1112119907794523</v>
       </c>
       <c r="J2" t="n">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="K2" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0182137850374452</v>
+        <v>0.01353938890190587</v>
       </c>
       <c r="M2" t="n">
-        <v>5.445780503721712</v>
+        <v>5.475257811270516</v>
       </c>
       <c r="N2" t="n">
-        <v>44.24546691382827</v>
+        <v>45.06140814090029</v>
       </c>
       <c r="O2" t="n">
-        <v>6.651726611476772</v>
+        <v>6.712779464640581</v>
       </c>
       <c r="P2" t="n">
-        <v>384.4978886313349</v>
+        <v>384.6911696260075</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -13989,28 +14075,28 @@
         <v>0.0731</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1491570181222614</v>
+        <v>0.1304017694219058</v>
       </c>
       <c r="J3" t="n">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="K3" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04687833394448537</v>
+        <v>0.03476872643798556</v>
       </c>
       <c r="M3" t="n">
-        <v>3.926690812655828</v>
+        <v>3.979037320434778</v>
       </c>
       <c r="N3" t="n">
-        <v>22.46015098034869</v>
+        <v>23.60643543184937</v>
       </c>
       <c r="O3" t="n">
-        <v>4.739214173293785</v>
+        <v>4.858645431789541</v>
       </c>
       <c r="P3" t="n">
-        <v>379.7126034008214</v>
+        <v>379.9213989800566</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -14067,28 +14153,28 @@
         <v>0.0895</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0370737730453006</v>
+        <v>0.01916522755014371</v>
       </c>
       <c r="J4" t="n">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="K4" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00293976182785427</v>
+        <v>0.0007588472990045503</v>
       </c>
       <c r="M4" t="n">
-        <v>3.904159543808001</v>
+        <v>3.961961802349676</v>
       </c>
       <c r="N4" t="n">
-        <v>23.14685215424266</v>
+        <v>24.1860375222609</v>
       </c>
       <c r="O4" t="n">
-        <v>4.811117557724262</v>
+        <v>4.917930207136017</v>
       </c>
       <c r="P4" t="n">
-        <v>386.09878176805</v>
+        <v>386.2981472746921</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14145,28 +14231,28 @@
         <v>0.0728</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02687626950658366</v>
+        <v>0.01199482019132709</v>
       </c>
       <c r="J5" t="n">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="K5" t="n">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001034023282532437</v>
+        <v>0.0002040585314804222</v>
       </c>
       <c r="M5" t="n">
-        <v>4.874816130442828</v>
+        <v>4.909607426991409</v>
       </c>
       <c r="N5" t="n">
-        <v>35.0343786838242</v>
+        <v>35.63960847447776</v>
       </c>
       <c r="O5" t="n">
-        <v>5.918984599052797</v>
+        <v>5.969891831053371</v>
       </c>
       <c r="P5" t="n">
-        <v>383.836971984041</v>
+        <v>384.0014617606491</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14223,28 +14309,28 @@
         <v>0.0607</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.134150166799119</v>
+        <v>-0.1464762582538254</v>
       </c>
       <c r="J6" t="n">
+        <v>307</v>
+      </c>
+      <c r="K6" t="n">
         <v>305</v>
       </c>
-      <c r="K6" t="n">
-        <v>303</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.0261105296341545</v>
+        <v>0.03088262882506199</v>
       </c>
       <c r="M6" t="n">
-        <v>4.727605333971325</v>
+        <v>4.749874106766027</v>
       </c>
       <c r="N6" t="n">
-        <v>32.79613393339429</v>
+        <v>33.13250743783215</v>
       </c>
       <c r="O6" t="n">
-        <v>5.726790893108835</v>
+        <v>5.756084384182719</v>
       </c>
       <c r="P6" t="n">
-        <v>388.8390040587905</v>
+        <v>388.9775492720319</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -14301,28 +14387,28 @@
         <v>0.0832</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.08614813191356865</v>
+        <v>-0.0957989024621001</v>
       </c>
       <c r="J7" t="n">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="K7" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01465006195834961</v>
+        <v>0.0180443987661858</v>
       </c>
       <c r="M7" t="n">
-        <v>4.079365039568185</v>
+        <v>4.099446655198101</v>
       </c>
       <c r="N7" t="n">
-        <v>24.75700815541483</v>
+        <v>24.94607134096982</v>
       </c>
       <c r="O7" t="n">
-        <v>4.975641481800596</v>
+        <v>4.994604222655667</v>
       </c>
       <c r="P7" t="n">
-        <v>387.1439290566775</v>
+        <v>387.251425649126</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -14379,28 +14465,28 @@
         <v>0.079</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1921783857859222</v>
+        <v>-0.1972684165033656</v>
       </c>
       <c r="J8" t="n">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="K8" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0463157142530144</v>
+        <v>0.04915898871775881</v>
       </c>
       <c r="M8" t="n">
-        <v>5.13932522329311</v>
+        <v>5.13163123342773</v>
       </c>
       <c r="N8" t="n">
-        <v>37.71731265920013</v>
+        <v>37.59687420600389</v>
       </c>
       <c r="O8" t="n">
-        <v>6.141442229574428</v>
+        <v>6.131629001008124</v>
       </c>
       <c r="P8" t="n">
-        <v>393.6327640416912</v>
+        <v>393.6894496254428</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -14438,7 +14524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I306"/>
+  <dimension ref="A1:I308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28795,6 +28881,100 @@
         </is>
       </c>
     </row>
+    <row r="307">
+      <c r="A307" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>-36.168589961546274,175.4843171394544</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>-36.16873874794867,175.48519962960916</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>-36.16880550085632,175.48608356429983</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>-36.16877420270844,175.4869605326666</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>-36.16866675310441,175.48783608013713</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>-36.16849496359725,175.4886895946666</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>-36.16822854319244,175.4895203241144</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:05:44+00:00</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>-36.168571892355565,175.48431983084097</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>-36.1687154011169,175.4852031069267</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>-36.168772808195,175.48608475000842</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>-36.16874837378838,175.48695745510355</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>-36.16864391519003,175.48783073090107</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>-36.168471505299394,175.48868123731444</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>-36.16819087568677,175.489505076623</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0118/nzd0118.xlsx
+++ b/data/nzd0118/nzd0118.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I308"/>
+  <dimension ref="A1:I309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10592,6 +10592,39 @@
       <c r="I308" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:05:46+00:00</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>375.92</v>
+      </c>
+      <c r="C309" t="n">
+        <v>373.75</v>
+      </c>
+      <c r="D309" t="n">
+        <v>379.09</v>
+      </c>
+      <c r="E309" t="n">
+        <v>376.66</v>
+      </c>
+      <c r="F309" t="n">
+        <v>380.53</v>
+      </c>
+      <c r="G309" t="n">
+        <v>381.22</v>
+      </c>
+      <c r="H309" t="n">
+        <v>388.37</v>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -10606,7 +10639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B322"/>
+  <dimension ref="A1:B323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13829,6 +13862,16 @@
       </c>
       <c r="B322" t="n">
         <v>0.5</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>0.53</v>
       </c>
     </row>
   </sheetData>
@@ -13997,28 +14040,28 @@
         <v>0.0478</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1112119907794523</v>
+        <v>0.1034450586582357</v>
       </c>
       <c r="J2" t="n">
+        <v>308</v>
+      </c>
+      <c r="K2" t="n">
         <v>307</v>
       </c>
-      <c r="K2" t="n">
-        <v>306</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.01353938890190587</v>
+        <v>0.01170171105238671</v>
       </c>
       <c r="M2" t="n">
-        <v>5.475257811270516</v>
+        <v>5.486240998135581</v>
       </c>
       <c r="N2" t="n">
-        <v>45.06140814090029</v>
+        <v>45.35575631670751</v>
       </c>
       <c r="O2" t="n">
-        <v>6.712779464640581</v>
+        <v>6.734668241027728</v>
       </c>
       <c r="P2" t="n">
-        <v>384.6911696260075</v>
+        <v>384.7780893103352</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -14075,28 +14118,28 @@
         <v>0.0731</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1304017694219058</v>
+        <v>0.1240247913626016</v>
       </c>
       <c r="J3" t="n">
+        <v>308</v>
+      </c>
+      <c r="K3" t="n">
         <v>307</v>
       </c>
-      <c r="K3" t="n">
-        <v>306</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.03476872643798556</v>
+        <v>0.03138168057555113</v>
       </c>
       <c r="M3" t="n">
-        <v>3.979037320434778</v>
+        <v>3.99253452416984</v>
       </c>
       <c r="N3" t="n">
-        <v>23.60643543184937</v>
+        <v>23.82691034475908</v>
       </c>
       <c r="O3" t="n">
-        <v>4.858645431789541</v>
+        <v>4.88128162932227</v>
       </c>
       <c r="P3" t="n">
-        <v>379.9213989800566</v>
+        <v>379.9927636979695</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -14153,28 +14196,28 @@
         <v>0.0895</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01916522755014371</v>
+        <v>0.01404166062789163</v>
       </c>
       <c r="J4" t="n">
+        <v>308</v>
+      </c>
+      <c r="K4" t="n">
         <v>307</v>
       </c>
-      <c r="K4" t="n">
-        <v>306</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.0007588472990045503</v>
+        <v>0.000407044712958049</v>
       </c>
       <c r="M4" t="n">
-        <v>3.961961802349676</v>
+        <v>3.972869151420801</v>
       </c>
       <c r="N4" t="n">
-        <v>24.1860375222609</v>
+        <v>24.29921550735033</v>
       </c>
       <c r="O4" t="n">
-        <v>4.917930207136017</v>
+        <v>4.929423445733824</v>
       </c>
       <c r="P4" t="n">
-        <v>386.2981472746921</v>
+        <v>386.3554850771299</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14231,28 +14274,28 @@
         <v>0.0728</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01199482019132709</v>
+        <v>0.006956177745470918</v>
       </c>
       <c r="J5" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K5" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002040585314804222</v>
+        <v>6.874225810493684e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>4.909607426991409</v>
+        <v>4.916116309869389</v>
       </c>
       <c r="N5" t="n">
-        <v>35.63960847447776</v>
+        <v>35.71249938644844</v>
       </c>
       <c r="O5" t="n">
-        <v>5.969891831053371</v>
+        <v>5.975993589893521</v>
       </c>
       <c r="P5" t="n">
-        <v>384.0014617606491</v>
+        <v>384.0574509706726</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14309,28 +14352,28 @@
         <v>0.0607</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1464762582538254</v>
+        <v>-0.1495644063237246</v>
       </c>
       <c r="J6" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K6" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03088262882506199</v>
+        <v>0.03230712620199805</v>
       </c>
       <c r="M6" t="n">
-        <v>4.749874106766027</v>
+        <v>4.747503863188474</v>
       </c>
       <c r="N6" t="n">
-        <v>33.13250743783215</v>
+        <v>33.09229432335592</v>
       </c>
       <c r="O6" t="n">
-        <v>5.756084384182719</v>
+        <v>5.752590227311165</v>
       </c>
       <c r="P6" t="n">
-        <v>388.9775492720319</v>
+        <v>389.0124401281167</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -14387,28 +14430,28 @@
         <v>0.0832</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0957989024621001</v>
+        <v>-0.09812957203820198</v>
       </c>
       <c r="J7" t="n">
+        <v>308</v>
+      </c>
+      <c r="K7" t="n">
         <v>307</v>
       </c>
-      <c r="K7" t="n">
-        <v>306</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.0180443987661858</v>
+        <v>0.01901397013588069</v>
       </c>
       <c r="M7" t="n">
-        <v>4.099446655198101</v>
+        <v>4.097226093688493</v>
       </c>
       <c r="N7" t="n">
-        <v>24.94607134096982</v>
+        <v>24.90446060451515</v>
       </c>
       <c r="O7" t="n">
-        <v>4.994604222655667</v>
+        <v>4.990436915192411</v>
       </c>
       <c r="P7" t="n">
-        <v>387.251425649126</v>
+        <v>387.2775232195553</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -14465,28 +14508,28 @@
         <v>0.079</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1972684165033656</v>
+        <v>-0.1973540186356307</v>
       </c>
       <c r="J8" t="n">
+        <v>308</v>
+      </c>
+      <c r="K8" t="n">
         <v>307</v>
       </c>
-      <c r="K8" t="n">
-        <v>306</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.04915898871775881</v>
+        <v>0.04952067196815269</v>
       </c>
       <c r="M8" t="n">
-        <v>5.13163123342773</v>
+        <v>5.115344623443129</v>
       </c>
       <c r="N8" t="n">
-        <v>37.59687420600389</v>
+        <v>37.47446230076049</v>
       </c>
       <c r="O8" t="n">
-        <v>6.131629001008124</v>
+        <v>6.121638857427028</v>
       </c>
       <c r="P8" t="n">
-        <v>393.6894496254428</v>
+        <v>393.6904081515671</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -14524,7 +14567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I308"/>
+  <dimension ref="A1:I309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28975,6 +29018,53 @@
         </is>
       </c>
     </row>
+    <row r="309">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:05:46+00:00</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>-36.168570640035405,175.48432001737265</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>-36.16868883403235,175.48520706387222</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>-36.168739395034116,175.4860859618481</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>-36.168730347354426,175.48695530722253</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>-36.16861656280362,175.4878243242625</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>-36.16845202885219,175.48867429855756</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>-36.168178804962785,175.48950019049835</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0118/nzd0118.xlsx
+++ b/data/nzd0118/nzd0118.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I309"/>
+  <dimension ref="A1:I310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10625,6 +10625,39 @@
       <c r="I309" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:05:37+00:00</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>377.77</v>
+      </c>
+      <c r="C310" t="n">
+        <v>374.96</v>
+      </c>
+      <c r="D310" t="n">
+        <v>380.56</v>
+      </c>
+      <c r="E310" t="n">
+        <v>377.84</v>
+      </c>
+      <c r="F310" t="n">
+        <v>381.27</v>
+      </c>
+      <c r="G310" t="n">
+        <v>381.9</v>
+      </c>
+      <c r="H310" t="n">
+        <v>388.95</v>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -10639,7 +10672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B323"/>
+  <dimension ref="A1:B324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13872,6 +13905,16 @@
       </c>
       <c r="B323" t="n">
         <v>0.53</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>-0.48</v>
       </c>
     </row>
   </sheetData>
@@ -14040,28 +14083,28 @@
         <v>0.0478</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1034450586582357</v>
+        <v>0.09703374907411375</v>
       </c>
       <c r="J2" t="n">
+        <v>309</v>
+      </c>
+      <c r="K2" t="n">
         <v>308</v>
       </c>
-      <c r="K2" t="n">
-        <v>307</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.01170171105238671</v>
+        <v>0.01031134473787532</v>
       </c>
       <c r="M2" t="n">
-        <v>5.486240998135581</v>
+        <v>5.492206814922298</v>
       </c>
       <c r="N2" t="n">
-        <v>45.35575631670751</v>
+        <v>45.51288884086989</v>
       </c>
       <c r="O2" t="n">
-        <v>6.734668241027728</v>
+        <v>6.746324098416107</v>
       </c>
       <c r="P2" t="n">
-        <v>384.7780893103352</v>
+        <v>384.8499054148993</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -14118,28 +14161,28 @@
         <v>0.0731</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1240247913626016</v>
+        <v>0.1185535209785222</v>
       </c>
       <c r="J3" t="n">
+        <v>309</v>
+      </c>
+      <c r="K3" t="n">
         <v>308</v>
       </c>
-      <c r="K3" t="n">
-        <v>307</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.03138168057555113</v>
+        <v>0.02868175580909749</v>
       </c>
       <c r="M3" t="n">
-        <v>3.99253452416984</v>
+        <v>4.002194881996778</v>
       </c>
       <c r="N3" t="n">
-        <v>23.82691034475908</v>
+        <v>23.97122454403745</v>
       </c>
       <c r="O3" t="n">
-        <v>4.88128162932227</v>
+        <v>4.896041722048276</v>
       </c>
       <c r="P3" t="n">
-        <v>379.9927636979695</v>
+        <v>380.0540499797885</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -14196,28 +14239,28 @@
         <v>0.0895</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01404166062789163</v>
+        <v>0.009982922630246889</v>
       </c>
       <c r="J4" t="n">
+        <v>309</v>
+      </c>
+      <c r="K4" t="n">
         <v>308</v>
       </c>
-      <c r="K4" t="n">
-        <v>307</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.000407044712958049</v>
+        <v>0.000206143459920094</v>
       </c>
       <c r="M4" t="n">
-        <v>3.972869151420801</v>
+        <v>3.978730490111468</v>
       </c>
       <c r="N4" t="n">
-        <v>24.29921550735033</v>
+        <v>24.34231104870985</v>
       </c>
       <c r="O4" t="n">
-        <v>4.929423445733824</v>
+        <v>4.933792765075348</v>
       </c>
       <c r="P4" t="n">
-        <v>386.3554850771299</v>
+        <v>386.400948917023</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14274,28 +14317,28 @@
         <v>0.0728</v>
       </c>
       <c r="I5" t="n">
-        <v>0.006956177745470918</v>
+        <v>0.002777244121835107</v>
       </c>
       <c r="J5" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K5" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L5" t="n">
-        <v>6.874225810493684e-05</v>
+        <v>1.0991712407038e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>4.916116309869389</v>
+        <v>4.918764934118022</v>
       </c>
       <c r="N5" t="n">
-        <v>35.71249938644844</v>
+        <v>35.72829723816719</v>
       </c>
       <c r="O5" t="n">
-        <v>5.975993589893521</v>
+        <v>5.977315219909954</v>
       </c>
       <c r="P5" t="n">
-        <v>384.0574509706726</v>
+        <v>384.1039309858814</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14352,28 +14395,28 @@
         <v>0.0607</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1495644063237246</v>
+        <v>-0.1521026949139426</v>
       </c>
       <c r="J6" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K6" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03230712620199805</v>
+        <v>0.0335515022427445</v>
       </c>
       <c r="M6" t="n">
-        <v>4.747503863188474</v>
+        <v>4.742996879380619</v>
       </c>
       <c r="N6" t="n">
-        <v>33.09229432335592</v>
+        <v>33.03107266158283</v>
       </c>
       <c r="O6" t="n">
-        <v>5.752590227311165</v>
+        <v>5.747266538240838</v>
       </c>
       <c r="P6" t="n">
-        <v>389.0124401281167</v>
+        <v>389.0411449668778</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -14430,28 +14473,28 @@
         <v>0.0832</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.09812957203820198</v>
+        <v>-0.09997316925579246</v>
       </c>
       <c r="J7" t="n">
+        <v>309</v>
+      </c>
+      <c r="K7" t="n">
         <v>308</v>
       </c>
-      <c r="K7" t="n">
-        <v>307</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.01901397013588069</v>
+        <v>0.01983278912675535</v>
       </c>
       <c r="M7" t="n">
-        <v>4.097226093688493</v>
+        <v>4.092683028357121</v>
       </c>
       <c r="N7" t="n">
-        <v>24.90446060451515</v>
+        <v>24.84872410518795</v>
       </c>
       <c r="O7" t="n">
-        <v>4.990436915192411</v>
+        <v>4.984849456622332</v>
       </c>
       <c r="P7" t="n">
-        <v>387.2775232195553</v>
+        <v>387.298186122617</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -14508,28 +14551,28 @@
         <v>0.079</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1973540186356307</v>
+        <v>-0.1970484035243379</v>
       </c>
       <c r="J8" t="n">
+        <v>309</v>
+      </c>
+      <c r="K8" t="n">
         <v>308</v>
       </c>
-      <c r="K8" t="n">
-        <v>307</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.04952067196815269</v>
+        <v>0.04969346278239095</v>
       </c>
       <c r="M8" t="n">
-        <v>5.115344623443129</v>
+        <v>5.100192964876196</v>
       </c>
       <c r="N8" t="n">
-        <v>37.47446230076049</v>
+        <v>37.3534823263179</v>
       </c>
       <c r="O8" t="n">
-        <v>6.121638857427028</v>
+        <v>6.111749530725053</v>
       </c>
       <c r="P8" t="n">
-        <v>393.6904081515671</v>
+        <v>393.6869828397047</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -14567,7 +14610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I309"/>
+  <dimension ref="A1:I310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29065,6 +29108,53 @@
         </is>
       </c>
     </row>
+    <row r="310">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:05:37+00:00</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>-36.16855409151908,175.48432248225546</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>-36.16867801040529,175.48520867596054</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>-36.168726155857115,175.48608644201093</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>-36.168719764671756,175.48695404627802</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>-36.16861001239385,175.48782278998735</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>-36.16844614263691,175.48867220151175</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>-36.168173839700366,175.48949818060356</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0118/nzd0118.xlsx
+++ b/data/nzd0118/nzd0118.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I310"/>
+  <dimension ref="A1:I311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10656,6 +10656,39 @@
         <v>388.95</v>
       </c>
       <c r="I310" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>378.16</v>
+      </c>
+      <c r="C311" t="n">
+        <v>375.84</v>
+      </c>
+      <c r="D311" t="n">
+        <v>382.03</v>
+      </c>
+      <c r="E311" t="n">
+        <v>380.89</v>
+      </c>
+      <c r="F311" t="n">
+        <v>383.18</v>
+      </c>
+      <c r="G311" t="n">
+        <v>382</v>
+      </c>
+      <c r="H311" t="n">
+        <v>385.07</v>
+      </c>
+      <c r="I311" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -10672,7 +10705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B324"/>
+  <dimension ref="A1:B325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13915,6 +13948,16 @@
       </c>
       <c r="B324" t="n">
         <v>-0.48</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>-0.58</v>
       </c>
     </row>
   </sheetData>
@@ -14083,28 +14126,28 @@
         <v>0.0478</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09703374907411375</v>
+        <v>0.09091792688670375</v>
       </c>
       <c r="J2" t="n">
+        <v>310</v>
+      </c>
+      <c r="K2" t="n">
         <v>309</v>
       </c>
-      <c r="K2" t="n">
-        <v>308</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.01031134473787532</v>
+        <v>0.009071342953389294</v>
       </c>
       <c r="M2" t="n">
-        <v>5.492206814922298</v>
+        <v>5.496708335033906</v>
       </c>
       <c r="N2" t="n">
-        <v>45.51288884086989</v>
+        <v>45.64018889312466</v>
       </c>
       <c r="O2" t="n">
-        <v>6.746324098416107</v>
+        <v>6.755752281805829</v>
       </c>
       <c r="P2" t="n">
-        <v>384.8499054148993</v>
+        <v>384.918794270152</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -14161,28 +14204,28 @@
         <v>0.0731</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1185535209785222</v>
+        <v>0.1136930287211661</v>
       </c>
       <c r="J3" t="n">
+        <v>310</v>
+      </c>
+      <c r="K3" t="n">
         <v>309</v>
       </c>
-      <c r="K3" t="n">
-        <v>308</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.02868175580909749</v>
+        <v>0.02642951539582128</v>
       </c>
       <c r="M3" t="n">
-        <v>4.002194881996778</v>
+        <v>4.009548242663164</v>
       </c>
       <c r="N3" t="n">
-        <v>23.97122454403745</v>
+        <v>24.06708288269824</v>
       </c>
       <c r="O3" t="n">
-        <v>4.896041722048276</v>
+        <v>4.905821326006302</v>
       </c>
       <c r="P3" t="n">
-        <v>380.0540499797885</v>
+        <v>380.108798750651</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -14239,28 +14282,28 @@
         <v>0.0895</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009982922630246889</v>
+        <v>0.006922728954224906</v>
       </c>
       <c r="J4" t="n">
+        <v>310</v>
+      </c>
+      <c r="K4" t="n">
         <v>309</v>
       </c>
-      <c r="K4" t="n">
-        <v>308</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.000206143459920094</v>
+        <v>9.954194817085593e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>3.978730490111468</v>
+        <v>3.979763758807326</v>
       </c>
       <c r="N4" t="n">
-        <v>24.34231104870985</v>
+        <v>24.33228360437828</v>
       </c>
       <c r="O4" t="n">
-        <v>4.933792765075348</v>
+        <v>4.93277646000488</v>
       </c>
       <c r="P4" t="n">
-        <v>386.400948917023</v>
+        <v>386.4354190557439</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14317,28 +14360,28 @@
         <v>0.0728</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002777244121835107</v>
+        <v>0.0006269700913479069</v>
       </c>
       <c r="J5" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K5" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L5" t="n">
-        <v>1.0991712407038e-05</v>
+        <v>5.634826302225449e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>4.918764934118022</v>
+        <v>4.912292934881028</v>
       </c>
       <c r="N5" t="n">
-        <v>35.72829723816719</v>
+        <v>35.64752859414112</v>
       </c>
       <c r="O5" t="n">
-        <v>5.977315219909954</v>
+        <v>5.970555132828196</v>
       </c>
       <c r="P5" t="n">
-        <v>384.1039309858814</v>
+        <v>384.1279820661791</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14395,28 +14438,28 @@
         <v>0.0607</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1521026949139426</v>
+        <v>-0.153327659676491</v>
       </c>
       <c r="J6" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K6" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0335515022427445</v>
+        <v>0.03429324280440604</v>
       </c>
       <c r="M6" t="n">
-        <v>4.742996879380619</v>
+        <v>4.732800415929495</v>
       </c>
       <c r="N6" t="n">
-        <v>33.03107266158283</v>
+        <v>32.93458142135691</v>
       </c>
       <c r="O6" t="n">
-        <v>5.747266538240838</v>
+        <v>5.738865865426453</v>
       </c>
       <c r="P6" t="n">
-        <v>389.0411449668778</v>
+        <v>389.0550740305799</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -14473,28 +14516,28 @@
         <v>0.0832</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.09997316925579246</v>
+        <v>-0.1017231189294272</v>
       </c>
       <c r="J7" t="n">
+        <v>310</v>
+      </c>
+      <c r="K7" t="n">
         <v>309</v>
       </c>
-      <c r="K7" t="n">
-        <v>308</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.01983278912675535</v>
+        <v>0.0206389541455545</v>
       </c>
       <c r="M7" t="n">
-        <v>4.092683028357121</v>
+        <v>4.087624591920592</v>
       </c>
       <c r="N7" t="n">
-        <v>24.84872410518795</v>
+        <v>24.79074715130377</v>
       </c>
       <c r="O7" t="n">
-        <v>4.984849456622332</v>
+        <v>4.979030744161334</v>
       </c>
       <c r="P7" t="n">
-        <v>387.298186122617</v>
+        <v>387.317908835956</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -14551,28 +14594,28 @@
         <v>0.079</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1970484035243379</v>
+        <v>-0.1992949622215693</v>
       </c>
       <c r="J8" t="n">
+        <v>310</v>
+      </c>
+      <c r="K8" t="n">
         <v>309</v>
       </c>
-      <c r="K8" t="n">
-        <v>308</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.04969346278239095</v>
+        <v>0.0510590210886791</v>
       </c>
       <c r="M8" t="n">
-        <v>5.100192964876196</v>
+        <v>5.094921875944683</v>
       </c>
       <c r="N8" t="n">
-        <v>37.3534823263179</v>
+        <v>37.26958009623557</v>
       </c>
       <c r="O8" t="n">
-        <v>6.111749530725053</v>
+        <v>6.104881661116419</v>
       </c>
       <c r="P8" t="n">
-        <v>393.6869828397047</v>
+        <v>393.7123025582383</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -14610,7 +14653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I310"/>
+  <dimension ref="A1:I311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29155,6 +29198,53 @@
         </is>
       </c>
     </row>
+    <row r="311">
+      <c r="A311" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>-36.16855060291293,175.4843230018793</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>-36.16867013867649,175.4852098483882</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>-36.168712916680086,175.48608692217374</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>-36.16869241112736,175.486950787059</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>-36.16859310525492,175.48781882990008</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>-36.16844527701701,175.48867189312267</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>-36.16820705559295,175.4895116261117</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0118/nzd0118.xlsx
+++ b/data/nzd0118/nzd0118.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I311"/>
+  <dimension ref="A1:I312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10691,6 +10691,39 @@
       <c r="I311" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:04:56+00:00</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>377.42</v>
+      </c>
+      <c r="C312" t="n">
+        <v>376.89</v>
+      </c>
+      <c r="D312" t="n">
+        <v>383.12</v>
+      </c>
+      <c r="E312" t="n">
+        <v>381.43</v>
+      </c>
+      <c r="F312" t="n">
+        <v>381.37</v>
+      </c>
+      <c r="G312" t="n">
+        <v>381.57</v>
+      </c>
+      <c r="H312" t="n">
+        <v>385.02</v>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -10705,7 +10738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B325"/>
+  <dimension ref="A1:B326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13958,6 +13991,16 @@
       </c>
       <c r="B325" t="n">
         <v>-0.58</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>-0.65</v>
       </c>
     </row>
   </sheetData>
@@ -14126,28 +14169,28 @@
         <v>0.0478</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09091792688670375</v>
+        <v>0.08436545602101933</v>
       </c>
       <c r="J2" t="n">
+        <v>311</v>
+      </c>
+      <c r="K2" t="n">
         <v>310</v>
       </c>
-      <c r="K2" t="n">
-        <v>309</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.009071342953389294</v>
+        <v>0.007821068502776862</v>
       </c>
       <c r="M2" t="n">
-        <v>5.496708335033906</v>
+        <v>5.50245721887476</v>
       </c>
       <c r="N2" t="n">
-        <v>45.64018889312466</v>
+        <v>45.80687340673286</v>
       </c>
       <c r="O2" t="n">
-        <v>6.755752281805829</v>
+        <v>6.76807752664912</v>
       </c>
       <c r="P2" t="n">
-        <v>384.918794270152</v>
+        <v>384.9929386984103</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -14204,28 +14247,28 @@
         <v>0.0731</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1136930287211661</v>
+        <v>0.1095660402529258</v>
       </c>
       <c r="J3" t="n">
+        <v>311</v>
+      </c>
+      <c r="K3" t="n">
         <v>310</v>
       </c>
-      <c r="K3" t="n">
-        <v>309</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.02642951539582128</v>
+        <v>0.02463362620549736</v>
       </c>
       <c r="M3" t="n">
-        <v>4.009548242663164</v>
+        <v>4.013848704969493</v>
       </c>
       <c r="N3" t="n">
-        <v>24.06708288269824</v>
+        <v>24.11397390914661</v>
       </c>
       <c r="O3" t="n">
-        <v>4.905821326006302</v>
+        <v>4.910598121323574</v>
       </c>
       <c r="P3" t="n">
-        <v>380.108798750651</v>
+        <v>380.1554976535043</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -14282,28 +14325,28 @@
         <v>0.0895</v>
       </c>
       <c r="I4" t="n">
-        <v>0.006922728954224906</v>
+        <v>0.00460717582079101</v>
       </c>
       <c r="J4" t="n">
+        <v>311</v>
+      </c>
+      <c r="K4" t="n">
         <v>310</v>
       </c>
-      <c r="K4" t="n">
-        <v>309</v>
-      </c>
       <c r="L4" t="n">
-        <v>9.954194817085593e-05</v>
+        <v>4.432479121385668e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>3.979763758807326</v>
+        <v>3.977299078620125</v>
       </c>
       <c r="N4" t="n">
-        <v>24.33228360437828</v>
+        <v>24.29299414281319</v>
       </c>
       <c r="O4" t="n">
-        <v>4.93277646000488</v>
+        <v>4.928792361503291</v>
       </c>
       <c r="P4" t="n">
-        <v>386.4354190557439</v>
+        <v>386.4616206774983</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14360,28 +14403,28 @@
         <v>0.0728</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0006269700913479069</v>
+        <v>-0.001150129692490767</v>
       </c>
       <c r="J5" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K5" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L5" t="n">
-        <v>5.634826302225449e-07</v>
+        <v>1.908014701568206e-06</v>
       </c>
       <c r="M5" t="n">
-        <v>4.912292934881028</v>
+        <v>4.904153688453608</v>
       </c>
       <c r="N5" t="n">
-        <v>35.64752859414112</v>
+        <v>35.5563637892275</v>
       </c>
       <c r="O5" t="n">
-        <v>5.970555132828196</v>
+        <v>5.962915712068007</v>
       </c>
       <c r="P5" t="n">
-        <v>384.1279820661791</v>
+        <v>384.1479507341205</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14438,28 +14481,28 @@
         <v>0.0607</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.153327659676491</v>
+        <v>-0.1557478661430746</v>
       </c>
       <c r="J6" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K6" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03429324280440604</v>
+        <v>0.03554069233629276</v>
       </c>
       <c r="M6" t="n">
-        <v>4.732800415929495</v>
+        <v>4.727689125323581</v>
       </c>
       <c r="N6" t="n">
-        <v>32.93458142135691</v>
+        <v>32.86979848577138</v>
       </c>
       <c r="O6" t="n">
-        <v>5.738865865426453</v>
+        <v>5.733218859050418</v>
       </c>
       <c r="P6" t="n">
-        <v>389.0550740305799</v>
+        <v>389.08271807583</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -14516,28 +14559,28 @@
         <v>0.0832</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1017231189294272</v>
+        <v>-0.1037341936768951</v>
       </c>
       <c r="J7" t="n">
+        <v>311</v>
+      </c>
+      <c r="K7" t="n">
         <v>310</v>
       </c>
-      <c r="K7" t="n">
-        <v>309</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.0206389541455545</v>
+        <v>0.02156591407130559</v>
       </c>
       <c r="M7" t="n">
-        <v>4.087624591920592</v>
+        <v>4.083721034016051</v>
       </c>
       <c r="N7" t="n">
-        <v>24.79074715130377</v>
+        <v>24.74029205331024</v>
       </c>
       <c r="O7" t="n">
-        <v>4.979030744161334</v>
+        <v>4.973961404485387</v>
       </c>
       <c r="P7" t="n">
-        <v>387.317908835956</v>
+        <v>387.340677943428</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -14594,28 +14637,28 @@
         <v>0.079</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1992949622215693</v>
+        <v>-0.2015413093871976</v>
       </c>
       <c r="J8" t="n">
+        <v>311</v>
+      </c>
+      <c r="K8" t="n">
         <v>310</v>
       </c>
-      <c r="K8" t="n">
-        <v>309</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.0510590210886791</v>
+        <v>0.05245005374674339</v>
       </c>
       <c r="M8" t="n">
-        <v>5.094921875944683</v>
+        <v>5.089566754931563</v>
       </c>
       <c r="N8" t="n">
-        <v>37.26958009623557</v>
+        <v>37.18618048783401</v>
       </c>
       <c r="O8" t="n">
-        <v>6.104881661116419</v>
+        <v>6.09804726841585</v>
       </c>
       <c r="P8" t="n">
-        <v>393.7123025582383</v>
+        <v>393.7377353871762</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -14653,7 +14696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I311"/>
+  <dimension ref="A1:I312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29245,6 +29288,53 @@
         </is>
       </c>
     </row>
+    <row r="312">
+      <c r="A312" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:04:56+00:00</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>-36.168557222319464,175.48432201592635</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>-36.1686607462728,175.4852112473073</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>-36.16870309987536,175.4860872782128</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>-36.16868756820471,175.48695021001723</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>-36.16860912720333,175.4878225826529</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>-36.168448999182566,175.48867321919568</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>-36.168207483632784,175.48951179937865</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0118/nzd0118.xlsx
+++ b/data/nzd0118/nzd0118.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I312"/>
+  <dimension ref="A1:I314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10722,6 +10722,72 @@
         <v>385.02</v>
       </c>
       <c r="I312" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:04:54+00:00</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>377.55</v>
+      </c>
+      <c r="C313" t="n">
+        <v>376.76</v>
+      </c>
+      <c r="D313" t="n">
+        <v>384.67</v>
+      </c>
+      <c r="E313" t="n">
+        <v>381.66</v>
+      </c>
+      <c r="F313" t="n">
+        <v>379.22</v>
+      </c>
+      <c r="G313" t="n">
+        <v>382.02</v>
+      </c>
+      <c r="H313" t="n">
+        <v>387.74</v>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:06+00:00</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>376.75</v>
+      </c>
+      <c r="C314" t="n">
+        <v>376.27</v>
+      </c>
+      <c r="D314" t="n">
+        <v>383.7</v>
+      </c>
+      <c r="E314" t="n">
+        <v>380.53</v>
+      </c>
+      <c r="F314" t="n">
+        <v>377.87</v>
+      </c>
+      <c r="G314" t="n">
+        <v>380.99</v>
+      </c>
+      <c r="H314" t="n">
+        <v>387.37</v>
+      </c>
+      <c r="I314" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -10738,7 +10804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B326"/>
+  <dimension ref="A1:B328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14001,6 +14067,26 @@
       </c>
       <c r="B326" t="n">
         <v>-0.65</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>-0.68</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>-0.7</v>
       </c>
     </row>
   </sheetData>
@@ -14169,28 +14255,28 @@
         <v>0.0478</v>
       </c>
       <c r="I2" t="n">
-        <v>0.08436545602101933</v>
+        <v>0.07120857464323423</v>
       </c>
       <c r="J2" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K2" t="n">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007821068502776862</v>
+        <v>0.00558301398496952</v>
       </c>
       <c r="M2" t="n">
-        <v>5.50245721887476</v>
+        <v>5.514065358411499</v>
       </c>
       <c r="N2" t="n">
-        <v>45.80687340673286</v>
+        <v>46.15416196777161</v>
       </c>
       <c r="O2" t="n">
-        <v>6.76807752664912</v>
+        <v>6.793685448103379</v>
       </c>
       <c r="P2" t="n">
-        <v>384.9929386984103</v>
+        <v>385.142224207358</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -14247,28 +14333,28 @@
         <v>0.0731</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1095660402529258</v>
+        <v>0.1010129834932123</v>
       </c>
       <c r="J3" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K3" t="n">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02463362620549736</v>
+        <v>0.02106670619941298</v>
       </c>
       <c r="M3" t="n">
-        <v>4.013848704969493</v>
+        <v>4.023989575341389</v>
       </c>
       <c r="N3" t="n">
-        <v>24.11397390914661</v>
+        <v>24.23021812161329</v>
       </c>
       <c r="O3" t="n">
-        <v>4.910598121323574</v>
+        <v>4.922419945678476</v>
       </c>
       <c r="P3" t="n">
-        <v>380.1554976535043</v>
+        <v>380.2525453708211</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -14325,28 +14411,28 @@
         <v>0.0895</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00460717582079101</v>
+        <v>0.00147653100821703</v>
       </c>
       <c r="J4" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K4" t="n">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="L4" t="n">
-        <v>4.432479121385668e-05</v>
+        <v>4.608537881645169e-06</v>
       </c>
       <c r="M4" t="n">
-        <v>3.977299078620125</v>
+        <v>3.96566913389906</v>
       </c>
       <c r="N4" t="n">
-        <v>24.29299414281319</v>
+        <v>24.17499798885983</v>
       </c>
       <c r="O4" t="n">
-        <v>4.928792361503291</v>
+        <v>4.91680770305895</v>
       </c>
       <c r="P4" t="n">
-        <v>386.4616206774983</v>
+        <v>386.4971480524543</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14403,28 +14489,28 @@
         <v>0.0728</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.001150129692490767</v>
+        <v>-0.00505383234386141</v>
       </c>
       <c r="J5" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K5" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="L5" t="n">
-        <v>1.908014701568206e-06</v>
+        <v>3.72838012223653e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>4.904153688453608</v>
+        <v>4.889411659672857</v>
       </c>
       <c r="N5" t="n">
-        <v>35.5563637892275</v>
+        <v>35.38837092406652</v>
       </c>
       <c r="O5" t="n">
-        <v>5.962915712068007</v>
+        <v>5.948812564206954</v>
       </c>
       <c r="P5" t="n">
-        <v>384.1479507341205</v>
+        <v>384.191942754875</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14481,28 +14567,28 @@
         <v>0.0607</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1557478661430746</v>
+        <v>-0.1641926428043986</v>
       </c>
       <c r="J6" t="n">
+        <v>313</v>
+      </c>
+      <c r="K6" t="n">
         <v>311</v>
       </c>
-      <c r="K6" t="n">
-        <v>309</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.03554069233629276</v>
+        <v>0.03956739622838934</v>
       </c>
       <c r="M6" t="n">
-        <v>4.727689125323581</v>
+        <v>4.733117103866118</v>
       </c>
       <c r="N6" t="n">
-        <v>32.86979848577138</v>
+        <v>32.91858647678468</v>
       </c>
       <c r="O6" t="n">
-        <v>5.733218859050418</v>
+        <v>5.737472132985456</v>
       </c>
       <c r="P6" t="n">
-        <v>389.08271807583</v>
+        <v>389.179442677944</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -14559,28 +14645,28 @@
         <v>0.0832</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1037341936768951</v>
+        <v>-0.1077425403684232</v>
       </c>
       <c r="J7" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K7" t="n">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02156591407130559</v>
+        <v>0.02348215006672694</v>
       </c>
       <c r="M7" t="n">
-        <v>4.083721034016051</v>
+        <v>4.075872432292561</v>
       </c>
       <c r="N7" t="n">
-        <v>24.74029205331024</v>
+        <v>24.642655702796</v>
       </c>
       <c r="O7" t="n">
-        <v>4.973961404485387</v>
+        <v>4.964136954476175</v>
       </c>
       <c r="P7" t="n">
-        <v>387.340677943428</v>
+        <v>387.3861896815337</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -14637,28 +14723,28 @@
         <v>0.079</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2015413093871976</v>
+        <v>-0.202598982813024</v>
       </c>
       <c r="J8" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K8" t="n">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05245005374674339</v>
+        <v>0.05366024505585731</v>
       </c>
       <c r="M8" t="n">
-        <v>5.089566754931563</v>
+        <v>5.062089733228182</v>
       </c>
       <c r="N8" t="n">
-        <v>37.18618048783401</v>
+        <v>36.9521501662467</v>
       </c>
       <c r="O8" t="n">
-        <v>6.09804726841585</v>
+        <v>6.078828025717351</v>
       </c>
       <c r="P8" t="n">
-        <v>393.7377353871762</v>
+        <v>393.7497451217044</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -14696,7 +14782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I312"/>
+  <dimension ref="A1:I314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29335,6 +29421,100 @@
         </is>
       </c>
     </row>
+    <row r="313">
+      <c r="A313" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:04:54+00:00</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>-36.16855605945075,175.4843221891343</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>-36.16866190914183,175.48521107410778</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>-36.16868914019887,175.48608778450688</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>-36.168685505478386,175.4869499642402</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>-36.16862815879924,175.4878270403449</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>-36.168445103893035,175.48867183144486</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>-36.16818419826503,175.48950237366023</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:06+00:00</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>-36.16856321556593,175.4843211232391</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>-36.16866629226355,175.48521042127888</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>-36.16869787625449,175.4860874676648</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>-36.168695639742445,175.48695117175353</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>-36.16864010887092,175.4878298393621</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>-36.168454019777926,175.48867500785252</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>-36.16818736575998,175.48950365583482</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
